--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:51</t>
+    <t xml:space="preserve">2026-09-10 01:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
@@ -48,6 +48,9 @@
     <t xml:space="preserve">Illapel</t>
   </si>
   <si>
+    <t xml:space="preserve">Paihuano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Punitaqui</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paihuano</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:01</t>
+    <t xml:space="preserve">2026-09-18 11:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -582,16 +582,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4102</v>
+        <v>4105</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="7">
@@ -599,10 +599,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4304</v>
+        <v>4102</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2020</v>
@@ -619,13 +619,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4101</v>
+        <v>4304</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="9">
@@ -636,13 +636,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>4301</v>
+        <v>4101</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -653,13 +653,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>4103</v>
+        <v>4301</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.61</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="11">
@@ -670,13 +670,13 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>4202</v>
+        <v>4103</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="12">
@@ -687,13 +687,13 @@
         <v>15</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4203</v>
+        <v>4202</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -704,7 +704,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>4204</v>
+        <v>4203</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2020</v>
@@ -721,13 +721,13 @@
         <v>17</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>4302</v>
+        <v>4204</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="15">
@@ -738,13 +738,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>4305</v>
+        <v>4302</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2020</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.77</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="16">
@@ -755,10 +755,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>4105</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+        <v>4305</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1.77</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E16"/>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:09</t>
+    <t xml:space="preserve">2026-09-23 14:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:32</t>
+    <t xml:space="preserve">2026-10-02 15:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:49</t>
+    <t xml:space="preserve">2026-10-04 10:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezjov_a_2020_coquimbo.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:19</t>
+    <t xml:space="preserve">2026-10-05 15:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
